--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,766 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9623,0.0023,0.0261,0.0024</t>
-  </si>
-  <si>
-    <t>0.9316,0.0014,0.0142,0.0152</t>
-  </si>
-  <si>
-    <t>0.9463,0.0032,0.0319,0.0034</t>
-  </si>
-  <si>
-    <t>0.8687,0.0012,0.0041,0.1403</t>
-  </si>
-  <si>
-    <t>0.9593,0.0016,0.0016,0.0320</t>
-  </si>
-  <si>
-    <t>0.9075,0.0035,0.0064,0.0762</t>
-  </si>
-  <si>
-    <t>0.8757,0.0195,0.0104,0.0441</t>
-  </si>
-  <si>
-    <t>0.9423,0.0020,0.0019,0.0496</t>
-  </si>
-  <si>
-    <t>0.8576,0.0158,0.0094,0.0607</t>
-  </si>
-  <si>
-    <t>0.9386,0.0029,0.0030,0.0419</t>
-  </si>
-  <si>
-    <t>0.8879,0.0059,0.0077,0.0844</t>
-  </si>
-  <si>
-    <t>0.9191,0.0042,0.0167,0.0305</t>
-  </si>
-  <si>
-    <t>0.9527,0.0018,0.0503,0.0005</t>
-  </si>
-  <si>
-    <t>0.7649,0.0232,0.2629,0.0126</t>
-  </si>
-  <si>
-    <t>0.6724,0.0096,0.5522,0.0016</t>
-  </si>
-  <si>
-    <t>0.8897,0.0031,0.1701,0.0009</t>
-  </si>
-  <si>
-    <t>0.9642,0.0013,0.0308,0.0010</t>
-  </si>
-  <si>
-    <t>0.8213,0.1051,0.0269,0.0014</t>
-  </si>
-  <si>
-    <t>0.8382,0.0517,0.0568,0.0032</t>
-  </si>
-  <si>
-    <t>0.9749,0.0046,0.0079,0.0007</t>
-  </si>
-  <si>
-    <t>0.5016,0.3689,0.1392,0.0105</t>
-  </si>
-  <si>
-    <t>0.7166,0.2285,0.0369,0.0004</t>
-  </si>
-  <si>
-    <t>0.9065,0.0017,0.1052,0.0016</t>
-  </si>
-  <si>
-    <t>0.9704,0.0011,0.0256,0.0004</t>
-  </si>
-  <si>
-    <t>0.7133,0.0036,0.3500,0.0035</t>
-  </si>
-  <si>
-    <t>0.9423,0.0044,0.0512,0.0014</t>
-  </si>
-  <si>
-    <t>0.6097,0.0109,0.6057,0.0011</t>
-  </si>
-  <si>
-    <t>0.7146,0.0054,0.5377,0.0011</t>
-  </si>
-  <si>
-    <t>0.3550,0.0038,0.8724,0.0007</t>
-  </si>
-  <si>
-    <t>0.9596,0.0050,0.0277,0.0018</t>
-  </si>
-  <si>
-    <t>0.9094,0.0111,0.0506,0.0089</t>
-  </si>
-  <si>
-    <t>0.0754,0.0900,0.9442,0.0017</t>
-  </si>
-  <si>
-    <t>0.7911,0.0565,0.1268,0.0014</t>
-  </si>
-  <si>
-    <t>0.9265,0.0065,0.0207,0.0084</t>
-  </si>
-  <si>
-    <t>0.8223,0.0029,0.1798,0.0084</t>
-  </si>
-  <si>
-    <t>0.9552,0.0084,0.0144,0.0033</t>
-  </si>
-  <si>
-    <t>0.9276,0.0212,0.0306,0.0017</t>
-  </si>
-  <si>
-    <t>0.5480,0.0691,0.5162,0.0056</t>
-  </si>
-  <si>
-    <t>0.1075,0.0034,0.9511,0.0004</t>
-  </si>
-  <si>
-    <t>0.9655,0.0004,0.0749,0.0001</t>
-  </si>
-  <si>
-    <t>0.4307,0.0013,0.7304,0.0011</t>
-  </si>
-  <si>
-    <t>0.6601,0.0090,0.5667,0.0006</t>
-  </si>
-  <si>
-    <t>0.0922,0.7152,0.4702,0.0029</t>
-  </si>
-  <si>
-    <t>0.5140,0.0238,0.6799,0.0022</t>
-  </si>
-  <si>
-    <t>0.9360,0.0058,0.0379,0.0029</t>
-  </si>
-  <si>
-    <t>0.9669,0.0063,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.9606,0.0069,0.0170,0.0003</t>
-  </si>
-  <si>
-    <t>0.9229,0.0278,0.0200,0.0004</t>
-  </si>
-  <si>
-    <t>0.2376,0.0407,0.8562,0.0015</t>
-  </si>
-  <si>
-    <t>0.0258,0.0506,0.9787,0.0003</t>
-  </si>
-  <si>
-    <t>0.7060,0.0068,0.3988,0.0043</t>
-  </si>
-  <si>
-    <t>0.7724,0.0007,0.3529,0.0009</t>
-  </si>
-  <si>
-    <t>0.1646,0.0111,0.9215,0.0018</t>
-  </si>
-  <si>
-    <t>0.8025,0.0049,0.4274,0.0004</t>
-  </si>
-  <si>
-    <t>0.9487,0.0051,0.0053,0.0248</t>
-  </si>
-  <si>
-    <t>0.9329,0.0037,0.0053,0.0299</t>
-  </si>
-  <si>
-    <t>0.9532,0.0050,0.0032,0.0182</t>
-  </si>
-  <si>
-    <t>0.5483,0.1817,0.4715,0.0389</t>
-  </si>
-  <si>
-    <t>0.9639,0.0019,0.0027,0.0194</t>
-  </si>
-  <si>
-    <t>0.8963,0.0026,0.0083,0.0779</t>
-  </si>
-  <si>
-    <t>0.9673,0.0061,0.0040,0.0048</t>
-  </si>
-  <si>
-    <t>0.0756,0.5223,0.8773,0.0052</t>
-  </si>
-  <si>
-    <t>0.4439,0.0318,0.7002,0.0012</t>
-  </si>
-  <si>
-    <t>0.5533,0.0089,0.6918,0.0003</t>
-  </si>
-  <si>
-    <t>0.0069,0.4148,0.9845,0.0003</t>
-  </si>
-  <si>
-    <t>0.2180,0.0132,0.8844,0.0003</t>
-  </si>
-  <si>
-    <t>0.4001,0.4892,0.1284,0.0019</t>
-  </si>
-  <si>
-    <t>0.1677,0.8949,0.0270,0.0004</t>
-  </si>
-  <si>
-    <t>0.9163,0.0057,0.0740,0.0041</t>
-  </si>
-  <si>
-    <t>0.7854,0.0054,0.2790,0.0033</t>
-  </si>
-  <si>
-    <t>0.0298,0.3896,0.9223,0.0027</t>
-  </si>
-  <si>
-    <t>0.1897,0.3001,0.7020,0.0009</t>
-  </si>
-  <si>
-    <t>0.4190,0.0482,0.7429,0.0007</t>
-  </si>
-  <si>
-    <t>0.1184,0.7588,0.4709,0.0043</t>
-  </si>
-  <si>
-    <t>0.0101,0.6326,0.9627,0.0025</t>
-  </si>
-  <si>
-    <t>0.9272,0.0005,0.0098,0.0273</t>
-  </si>
-  <si>
-    <t>0.8196,0.0003,0.0022,0.2132</t>
-  </si>
-  <si>
-    <t>0.8288,0.0004,0.0018,0.1779</t>
-  </si>
-  <si>
-    <t>0.9364,0.0018,0.0044,0.0355</t>
-  </si>
-  <si>
-    <t>0.7960,0.0009,0.0202,0.0964</t>
-  </si>
-  <si>
-    <t>0.9716,0.0001,0.0012,0.0143</t>
-  </si>
-  <si>
-    <t>0.1093,0.5142,0.8243,0.0021</t>
-  </si>
-  <si>
-    <t>0.1645,0.0324,0.9303,0.0003</t>
-  </si>
-  <si>
-    <t>0.8086,0.0143,0.2703,0.0008</t>
-  </si>
-  <si>
-    <t>0.0702,0.2671,0.9295,0.0019</t>
-  </si>
-  <si>
-    <t>0.2270,0.0842,0.8553,0.0007</t>
-  </si>
-  <si>
-    <t>0.4266,0.0607,0.6648,0.0006</t>
-  </si>
-  <si>
-    <t>0.9596,0.0044,0.0087,0.0068</t>
-  </si>
-  <si>
-    <t>0.9727,0.0043,0.0040,0.0051</t>
-  </si>
-  <si>
-    <t>0.9680,0.0039,0.0050,0.0094</t>
-  </si>
-  <si>
-    <t>0.9022,0.0048,0.0046,0.0739</t>
-  </si>
-  <si>
-    <t>0.9675,0.0034,0.0038,0.0111</t>
-  </si>
-  <si>
-    <t>0.9639,0.0020,0.0017,0.0247</t>
-  </si>
-  <si>
-    <t>0.9610,0.0065,0.0056,0.0060</t>
-  </si>
-  <si>
-    <t>0.9205,0.0197,0.0056,0.0169</t>
-  </si>
-  <si>
-    <t>0.9342,0.0031,0.0037,0.0453</t>
-  </si>
-  <si>
-    <t>0.9524,0.0048,0.0105,0.0208</t>
-  </si>
-  <si>
-    <t>0.9347,0.0007,0.0013,0.0745</t>
-  </si>
-  <si>
-    <t>0.9554,0.0022,0.0030,0.0272</t>
-  </si>
-  <si>
-    <t>0.8711,0.0049,0.0038,0.1247</t>
-  </si>
-  <si>
-    <t>0.8960,0.0267,0.0168,0.0155</t>
-  </si>
-  <si>
-    <t>0.9357,0.0043,0.0048,0.0401</t>
-  </si>
-  <si>
-    <t>0.9054,0.0039,0.0013,0.0622</t>
-  </si>
-  <si>
-    <t>0.0312,0.0087,0.9779,0.0020</t>
-  </si>
-  <si>
-    <t>0.7187,0.0241,0.3692,0.0028</t>
-  </si>
-  <si>
-    <t>0.9842,0.0003,0.0139,0.0002</t>
-  </si>
-  <si>
-    <t>0.9302,0.0025,0.1023,0.0009</t>
-  </si>
-  <si>
-    <t>0.7036,0.1897,0.0998,0.0095</t>
-  </si>
-  <si>
-    <t>0.8710,0.0363,0.0843,0.0049</t>
-  </si>
-  <si>
-    <t>0.5842,0.2275,0.2268,0.0078</t>
-  </si>
-  <si>
-    <t>0.8631,0.0364,0.0682,0.0065</t>
-  </si>
-  <si>
-    <t>0.8182,0.0595,0.0857,0.0040</t>
-  </si>
-  <si>
-    <t>0.5496,0.3769,0.0468,0.0026</t>
-  </si>
-  <si>
-    <t>0.8940,0.0147,0.0448,0.0134</t>
-  </si>
-  <si>
-    <t>0.9778,0.0010,0.0138,0.0008</t>
-  </si>
-  <si>
-    <t>0.8641,0.0034,0.1706,0.0032</t>
-  </si>
-  <si>
-    <t>0.9427,0.0018,0.0493,0.0013</t>
-  </si>
-  <si>
-    <t>0.8870,0.0045,0.0909,0.0057</t>
-  </si>
-  <si>
-    <t>0.7008,0.0142,0.2110,0.0334</t>
-  </si>
-  <si>
-    <t>0.9258,0.0208,0.0261,0.0006</t>
-  </si>
-  <si>
-    <t>0.8043,0.1662,0.0184,0.0024</t>
-  </si>
-  <si>
-    <t>0.8298,0.0180,0.1436,0.0075</t>
-  </si>
-  <si>
-    <t>0.4620,0.2886,0.2766,0.0025</t>
-  </si>
-  <si>
-    <t>0.9377,0.0125,0.0276,0.0018</t>
-  </si>
-  <si>
-    <t>0.8968,0.0359,0.0473,0.0030</t>
-  </si>
-  <si>
-    <t>0.8973,0.0292,0.0332,0.0074</t>
-  </si>
-  <si>
-    <t>0.9453,0.0054,0.0128,0.0133</t>
-  </si>
-  <si>
-    <t>0.9611,0.0034,0.0048,0.0147</t>
-  </si>
-  <si>
-    <t>0.8739,0.0114,0.0217,0.0737</t>
-  </si>
-  <si>
-    <t>0.9824,0.0039,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.8908,0.0095,0.0063,0.0621</t>
-  </si>
-  <si>
-    <t>0.9697,0.0024,0.0206,0.0023</t>
-  </si>
-  <si>
-    <t>0.8562,0.0077,0.0166,0.0711</t>
-  </si>
-  <si>
-    <t>0.8501,0.0119,0.0535,0.0412</t>
-  </si>
-  <si>
-    <t>0.1759,0.1106,0.9083,0.0013</t>
-  </si>
-  <si>
-    <t>0.5296,0.0341,0.6718,0.0005</t>
-  </si>
-  <si>
-    <t>0.6216,0.0062,0.5694,0.0007</t>
-  </si>
-  <si>
-    <t>0.6856,0.0067,0.5407,0.0007</t>
-  </si>
-  <si>
-    <t>0.9828,0.0004,0.0148,0.0003</t>
-  </si>
-  <si>
-    <t>0.9488,0.0018,0.0358,0.0026</t>
-  </si>
-  <si>
-    <t>0.9700,0.0003,0.0697,0.0001</t>
-  </si>
-  <si>
-    <t>0.9365,0.0016,0.0666,0.0009</t>
-  </si>
-  <si>
-    <t>0.9646,0.0001,0.0022,0.0120</t>
-  </si>
-  <si>
-    <t>0.7398,0.0008,0.0060,0.2729</t>
-  </si>
-  <si>
-    <t>0.4334,0.0011,0.0026,0.7374</t>
-  </si>
-  <si>
-    <t>0.9506,0.0009,0.0041,0.0260</t>
-  </si>
-  <si>
-    <t>0.0373,0.7228,0.8558,0.0031</t>
-  </si>
-  <si>
-    <t>0.9644,0.0018,0.0200,0.0037</t>
-  </si>
-  <si>
-    <t>0.9794,0.0042,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.9046,0.0074,0.0108,0.0817</t>
-  </si>
-  <si>
-    <t>0.7795,0.0818,0.0455,0.0220</t>
-  </si>
-  <si>
-    <t>0.9570,0.0042,0.0123,0.0099</t>
-  </si>
-  <si>
-    <t>0.9779,0.0006,0.0017,0.0115</t>
-  </si>
-  <si>
-    <t>0.9643,0.0037,0.0044,0.0072</t>
-  </si>
-  <si>
-    <t>0.4905,0.0717,0.5981,0.0367</t>
-  </si>
-  <si>
-    <t>0.9169,0.0058,0.0151,0.0220</t>
-  </si>
-  <si>
-    <t>0.9336,0.0084,0.0077,0.0306</t>
-  </si>
-  <si>
-    <t>0.9193,0.0096,0.0462,0.0049</t>
-  </si>
-  <si>
-    <t>0.9854,0.0003,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.9117,0.0070,0.0702,0.0049</t>
-  </si>
-  <si>
-    <t>0.9864,0.0014,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.8741,0.0201,0.0612,0.0104</t>
-  </si>
-  <si>
-    <t>0.9733,0.0013,0.0093,0.0026</t>
-  </si>
-  <si>
-    <t>0.9201,0.0012,0.0019,0.0905</t>
-  </si>
-  <si>
-    <t>0.9412,0.0021,0.0024,0.0560</t>
-  </si>
-  <si>
-    <t>0.9018,0.0044,0.0116,0.0398</t>
-  </si>
-  <si>
-    <t>0.9844,0.0016,0.0029,0.0027</t>
-  </si>
-  <si>
-    <t>0.8859,0.0199,0.0208,0.0306</t>
-  </si>
-  <si>
-    <t>0.8724,0.0167,0.0146,0.0455</t>
-  </si>
-  <si>
-    <t>0.9360,0.0057,0.0025,0.0333</t>
-  </si>
-  <si>
-    <t>0.9653,0.0041,0.0128,0.0076</t>
-  </si>
-  <si>
-    <t>0.8787,0.0268,0.0392,0.0134</t>
-  </si>
-  <si>
-    <t>0.9032,0.0184,0.0532,0.0059</t>
-  </si>
-  <si>
-    <t>0.9256,0.0161,0.0415,0.0052</t>
-  </si>
-  <si>
-    <t>0.5922,0.1552,0.3214,0.0204</t>
-  </si>
-  <si>
-    <t>0.9379,0.0098,0.0231,0.0063</t>
-  </si>
-  <si>
-    <t>0.9497,0.0052,0.0104,0.0138</t>
-  </si>
-  <si>
-    <t>0.9486,0.0037,0.0216,0.0077</t>
-  </si>
-  <si>
-    <t>0.9257,0.0131,0.0243,0.0081</t>
-  </si>
-  <si>
-    <t>0.1347,0.1786,0.9121,0.0142</t>
-  </si>
-  <si>
-    <t>0.9068,0.0074,0.0205,0.0229</t>
-  </si>
-  <si>
-    <t>0.2322,0.0089,0.8614,0.0030</t>
-  </si>
-  <si>
-    <t>0.5896,0.0046,0.7194,0.0003</t>
-  </si>
-  <si>
-    <t>0.9291,0.0024,0.0916,0.0014</t>
-  </si>
-  <si>
-    <t>0.3340,0.0321,0.8079,0.0024</t>
-  </si>
-  <si>
-    <t>0.7912,0.0029,0.3667,0.0010</t>
-  </si>
-  <si>
-    <t>0.0456,0.0114,0.9793,0.0003</t>
-  </si>
-  <si>
-    <t>0.4310,0.0239,0.7088,0.0028</t>
-  </si>
-  <si>
-    <t>0.9323,0.0017,0.0938,0.0005</t>
-  </si>
-  <si>
-    <t>0.9528,0.0011,0.0543,0.0006</t>
-  </si>
-  <si>
-    <t>0.9455,0.0012,0.0617,0.0009</t>
-  </si>
-  <si>
-    <t>0.8395,0.0065,0.2304,0.0014</t>
-  </si>
-  <si>
-    <t>0.9500,0.0092,0.0202,0.0020</t>
-  </si>
-  <si>
-    <t>0.9574,0.0019,0.0422,0.0006</t>
-  </si>
-  <si>
-    <t>0.9105,0.0037,0.0788,0.0034</t>
-  </si>
-  <si>
-    <t>0.8328,0.0034,0.1987,0.0029</t>
-  </si>
-  <si>
-    <t>0.8898,0.0291,0.0314,0.0196</t>
-  </si>
-  <si>
-    <t>0.9658,0.0216,0.0028,0.0021</t>
-  </si>
-  <si>
-    <t>0.9352,0.0116,0.0227,0.0088</t>
-  </si>
-  <si>
-    <t>0.9057,0.0063,0.0059,0.0424</t>
-  </si>
-  <si>
-    <t>0.9543,0.0070,0.0073,0.0113</t>
-  </si>
-  <si>
-    <t>0.9764,0.0004,0.0165,0.0007</t>
-  </si>
-  <si>
-    <t>0.9541,0.0010,0.0415,0.0006</t>
-  </si>
-  <si>
-    <t>0.9177,0.0013,0.0964,0.0016</t>
-  </si>
-  <si>
-    <t>0.9277,0.0031,0.0765,0.0013</t>
-  </si>
-  <si>
-    <t>0.6925,0.0012,0.4094,0.0030</t>
-  </si>
-  <si>
-    <t>0.7574,0.0027,0.4754,0.0005</t>
-  </si>
-  <si>
-    <t>0.5839,0.0208,0.6368,0.0019</t>
-  </si>
-  <si>
-    <t>0.3168,0.0511,0.7657,0.0019</t>
-  </si>
-  <si>
-    <t>0.7113,0.0186,0.4307,0.0011</t>
-  </si>
-  <si>
-    <t>0.3870,0.0041,0.7947,0.0007</t>
-  </si>
-  <si>
-    <t>0.8872,0.0039,0.0185,0.0670</t>
-  </si>
-  <si>
-    <t>0.8008,0.0352,0.0208,0.0734</t>
-  </si>
-  <si>
-    <t>0.9317,0.0084,0.0073,0.0197</t>
-  </si>
-  <si>
-    <t>0.8365,0.0050,0.0132,0.1570</t>
-  </si>
-  <si>
-    <t>0.9475,0.0070,0.0166,0.0084</t>
-  </si>
-  <si>
-    <t>0.9645,0.0035,0.0034,0.0152</t>
-  </si>
-  <si>
-    <t>0.9253,0.0075,0.0088,0.0281</t>
-  </si>
-  <si>
-    <t>0.8764,0.0189,0.0113,0.0411</t>
-  </si>
-  <si>
-    <t>0.7739,0.0033,0.2584,0.0068</t>
-  </si>
-  <si>
-    <t>0.8498,0.0086,0.0991,0.0129</t>
-  </si>
-  <si>
-    <t>0.8888,0.0018,0.0120,0.0486</t>
-  </si>
-  <si>
-    <t>0.1656,0.0054,0.9075,0.0018</t>
-  </si>
-  <si>
-    <t>0.0388,0.0027,0.9710,0.0005</t>
-  </si>
-  <si>
-    <t>0.8108,0.0035,0.3542,0.0010</t>
-  </si>
-  <si>
-    <t>0.0241,0.0125,0.9832,0.0007</t>
-  </si>
-  <si>
-    <t>0.9221,0.0036,0.1267,0.0008</t>
-  </si>
-  <si>
-    <t>0.0640,0.0113,0.9769,0.0007</t>
-  </si>
-  <si>
-    <t>0.4452,0.0115,0.7988,0.0007</t>
-  </si>
-  <si>
-    <t>0.9474,0.0030,0.0488,0.0012</t>
-  </si>
-  <si>
-    <t>0.9776,0.0005,0.0229,0.0003</t>
-  </si>
-  <si>
-    <t>0.9629,0.0009,0.0182,0.0026</t>
-  </si>
-  <si>
-    <t>0.9737,0.0005,0.0306,0.0003</t>
-  </si>
-  <si>
-    <t>0.9226,0.0084,0.0116,0.0292</t>
-  </si>
-  <si>
-    <t>0.9620,0.0016,0.0037,0.0184</t>
-  </si>
-  <si>
-    <t>0.9260,0.0170,0.0048,0.0128</t>
-  </si>
-  <si>
-    <t>0.9378,0.0044,0.0019,0.0312</t>
-  </si>
-  <si>
-    <t>0.8798,0.0047,0.0011,0.0670</t>
-  </si>
-  <si>
-    <t>0.9492,0.0031,0.0142,0.0124</t>
-  </si>
-  <si>
-    <t>0.9490,0.0020,0.0018,0.0400</t>
-  </si>
-  <si>
-    <t>0.8834,0.0064,0.0057,0.0726</t>
-  </si>
-  <si>
-    <t>0.7865,0.0133,0.3377,0.0006</t>
-  </si>
-  <si>
-    <t>0.2426,0.0571,0.8905,0.0017</t>
-  </si>
-  <si>
-    <t>0.3127,0.0208,0.8453,0.0017</t>
-  </si>
-  <si>
-    <t>0.8142,0.0046,0.2855,0.0015</t>
-  </si>
-  <si>
-    <t>0.1350,0.0131,0.9281,0.0012</t>
-  </si>
-  <si>
-    <t>0.9327,0.0005,0.0282,0.0051</t>
-  </si>
-  <si>
-    <t>0.9620,0.0003,0.0636,0.0002</t>
-  </si>
-  <si>
-    <t>0.1491,0.0092,0.8889,0.0040</t>
-  </si>
-  <si>
-    <t>0.9228,0.0011,0.0068,0.0317</t>
-  </si>
-  <si>
-    <t>0.9091,0.0002,0.0095,0.0191</t>
-  </si>
-  <si>
-    <t>0.9749,0.0001,0.0015,0.0066</t>
-  </si>
-  <si>
-    <t>0.7968,0.0003,0.0110,0.0923</t>
-  </si>
-  <si>
-    <t>0.6942,0.0006,0.0090,0.3042</t>
-  </si>
-  <si>
-    <t>0.9334,0.0007,0.0508,0.0020</t>
+    <t>0.9228,0.0054,0.0103,0.0522</t>
+  </si>
+  <si>
+    <t>0.2126,0.0023,0.0017,0.9240</t>
+  </si>
+  <si>
+    <t>0.9210,0.0143,0.0228,0.0333</t>
+  </si>
+  <si>
+    <t>0.3045,0.0057,0.0015,0.8382</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9937,0.0005,0.0000,0.0032</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0070,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0020,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.3506,0.0225,0.7339,0.0034</t>
+  </si>
+  <si>
+    <t>0.1611,0.0136,0.9096,0.0028</t>
+  </si>
+  <si>
+    <t>0.0327,0.0079,0.9768,0.0006</t>
+  </si>
+  <si>
+    <t>0.1713,0.0150,0.8218,0.0022</t>
+  </si>
+  <si>
+    <t>0.8452,0.0239,0.1147,0.0151</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0033,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0085,0.0006</t>
+  </si>
+  <si>
+    <t>0.0285,0.9761,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9969,0.0104,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.4998,0.0199,0.4331,0.0438</t>
+  </si>
+  <si>
+    <t>0.4351,0.0093,0.5655,0.0132</t>
+  </si>
+  <si>
+    <t>0.0019,0.0017,0.9943,0.0025</t>
+  </si>
+  <si>
+    <t>0.5932,0.0022,0.5437,0.0030</t>
+  </si>
+  <si>
+    <t>0.1067,0.0009,0.9396,0.0015</t>
+  </si>
+  <si>
+    <t>0.0211,0.0031,0.9840,0.0012</t>
+  </si>
+  <si>
+    <t>0.0012,0.0004,0.9975,0.0012</t>
+  </si>
+  <si>
+    <t>0.6517,0.2957,0.0626,0.0058</t>
+  </si>
+  <si>
+    <t>0.2477,0.4086,0.3852,0.0030</t>
+  </si>
+  <si>
+    <t>0.0085,0.0126,0.9890,0.0090</t>
+  </si>
+  <si>
+    <t>0.0052,0.6256,0.6078,0.0009</t>
+  </si>
+  <si>
+    <t>0.5194,0.5939,0.0100,0.0021</t>
+  </si>
+  <si>
+    <t>0.4567,0.0441,0.5412,0.0193</t>
+  </si>
+  <si>
+    <t>0.3076,0.8502,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0110,0.9797,0.1432,0.0026</t>
+  </si>
+  <si>
+    <t>0.0098,0.8726,0.0629,0.0943</t>
+  </si>
+  <si>
+    <t>0.0251,0.0175,0.9730,0.0047</t>
+  </si>
+  <si>
+    <t>0.0418,0.0047,0.9640,0.0011</t>
+  </si>
+  <si>
+    <t>0.0439,0.0011,0.9542,0.0051</t>
+  </si>
+  <si>
+    <t>0.0357,0.0946,0.9598,0.0030</t>
+  </si>
+  <si>
+    <t>0.0065,0.9456,0.1366,0.0005</t>
+  </si>
+  <si>
+    <t>0.0075,0.0394,0.9847,0.0019</t>
+  </si>
+  <si>
+    <t>0.2854,0.0773,0.0054,0.6527</t>
+  </si>
+  <si>
+    <t>0.0077,0.9394,0.0574,0.1082</t>
+  </si>
+  <si>
+    <t>0.0035,0.9907,0.0374,0.0012</t>
+  </si>
+  <si>
+    <t>0.0007,0.9960,0.0129,0.0041</t>
+  </si>
+  <si>
+    <t>0.0030,0.5691,0.9081,0.0044</t>
+  </si>
+  <si>
+    <t>0.0028,0.5437,0.9809,0.0019</t>
+  </si>
+  <si>
+    <t>0.0390,0.0100,0.9511,0.0030</t>
+  </si>
+  <si>
+    <t>0.0094,0.0007,0.9903,0.0013</t>
+  </si>
+  <si>
+    <t>0.0251,0.0268,0.9592,0.0116</t>
+  </si>
+  <si>
+    <t>0.0069,0.0039,0.9833,0.0012</t>
+  </si>
+  <si>
+    <t>0.9868,0.0143,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9913,0.0104,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0033,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0084,0.1191,0.9729,0.0204</t>
+  </si>
+  <si>
+    <t>0.9937,0.0069,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9882,0.0204,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0048,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.9725,0.9595,0.0007</t>
+  </si>
+  <si>
+    <t>0.0192,0.0333,0.9568,0.0060</t>
+  </si>
+  <si>
+    <t>0.0171,0.0717,0.9696,0.0101</t>
+  </si>
+  <si>
+    <t>0.0013,0.9260,0.9791,0.0008</t>
+  </si>
+  <si>
+    <t>0.0040,0.0007,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0040,0.9923,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.9953,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.8963,0.0181,0.1510,0.0034</t>
+  </si>
+  <si>
+    <t>0.0215,0.0291,0.9788,0.0025</t>
+  </si>
+  <si>
+    <t>0.0061,0.0034,0.9901,0.0076</t>
+  </si>
+  <si>
+    <t>0.0002,0.9882,0.9773,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9836,0.7795,0.0022</t>
+  </si>
+  <si>
+    <t>0.0006,0.9955,0.0260,0.0050</t>
+  </si>
+  <si>
+    <t>0.0024,0.9428,0.7710,0.0041</t>
+  </si>
+  <si>
+    <t>0.0078,0.0005,0.0202,0.9883</t>
+  </si>
+  <si>
+    <t>0.0009,0.0042,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0072,0.0020,0.0002,0.9969</t>
+  </si>
+  <si>
+    <t>0.0380,0.0038,0.0027,0.9820</t>
+  </si>
+  <si>
+    <t>0.0138,0.0010,0.0016,0.9940</t>
+  </si>
+  <si>
+    <t>0.0056,0.0013,0.0004,0.9975</t>
+  </si>
+  <si>
+    <t>0.0001,0.9935,0.9769,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.7707,0.9731,0.0011</t>
+  </si>
+  <si>
+    <t>0.0086,0.8547,0.8040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0032,0.4819,0.9605,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.9882,0.6916,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9377,0.9356,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0020,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0023,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9928,0.0050,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9917,0.0103,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9899,0.0070,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9959,0.0037,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0029,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0041,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.0368,0.0012,0.9766,0.0025</t>
+  </si>
+  <si>
+    <t>0.4455,0.0062,0.6776,0.0021</t>
+  </si>
+  <si>
+    <t>0.9852,0.0008,0.0091,0.0005</t>
+  </si>
+  <si>
+    <t>0.0281,0.0051,0.9579,0.0105</t>
+  </si>
+  <si>
+    <t>0.0089,0.9876,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.0015,0.9973,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0981,0.9096,0.0046,0.0039</t>
+  </si>
+  <si>
+    <t>0.0862,0.9334,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.9894,0.0019,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8841,0.1808,0.0044,0.0007</t>
+  </si>
+  <si>
+    <t>0.7755,0.0392,0.1783,0.0327</t>
+  </si>
+  <si>
+    <t>0.0941,0.0155,0.9277,0.0032</t>
+  </si>
+  <si>
+    <t>0.0467,0.1128,0.8165,0.0403</t>
+  </si>
+  <si>
+    <t>0.7081,0.0235,0.3375,0.0127</t>
+  </si>
+  <si>
+    <t>0.1439,0.0650,0.3832,0.5296</t>
+  </si>
+  <si>
+    <t>0.0011,0.9959,0.0072,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.9933,0.0079,0.0153</t>
+  </si>
+  <si>
+    <t>0.0004,0.9972,0.0041,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.9876,0.7849,0.0016</t>
+  </si>
+  <si>
+    <t>0.0132,0.9824,0.0061,0.0020</t>
+  </si>
+  <si>
+    <t>0.9630,0.0437,0.0054,0.0007</t>
+  </si>
+  <si>
+    <t>0.8779,0.1618,0.0072,0.0019</t>
+  </si>
+  <si>
+    <t>0.9958,0.0028,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9904,0.0073,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9859,0.0111,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9872,0.0106,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9877,0.0058,0.0020,0.0016</t>
+  </si>
+  <si>
+    <t>0.0044,0.7091,0.9848,0.0032</t>
+  </si>
+  <si>
+    <t>0.0099,0.8308,0.8197,0.0014</t>
+  </si>
+  <si>
+    <t>0.0051,0.0299,0.9828,0.0043</t>
+  </si>
+  <si>
+    <t>0.1824,0.0367,0.7896,0.0023</t>
+  </si>
+  <si>
+    <t>0.8913,0.0077,0.1364,0.0047</t>
+  </si>
+  <si>
+    <t>0.9023,0.0048,0.1283,0.0028</t>
+  </si>
+  <si>
+    <t>0.3267,0.0011,0.8769,0.0009</t>
+  </si>
+  <si>
+    <t>0.7672,0.0406,0.2139,0.0088</t>
+  </si>
+  <si>
+    <t>0.3343,0.0003,0.0017,0.8495</t>
+  </si>
+  <si>
+    <t>0.0003,0.0013,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0060,0.0008,0.0003,0.9975</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0013,0.9793,0.5658,0.0035</t>
+  </si>
+  <si>
+    <t>0.9944,0.0026,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.0037,0.9918,0.0019,0.0020</t>
+  </si>
+  <si>
+    <t>0.9950,0.0017,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9032,0.1536,0.0033,0.0028</t>
+  </si>
+  <si>
+    <t>0.9910,0.0041,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.5497,0.0013,0.0088,0.6040</t>
+  </si>
+  <si>
+    <t>0.9943,0.0023,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.0870,0.1528,0.8520,0.1436</t>
+  </si>
+  <si>
+    <t>0.9511,0.0003,0.0003,0.0956</t>
+  </si>
+  <si>
+    <t>0.9785,0.0046,0.0018,0.0095</t>
+  </si>
+  <si>
+    <t>0.5128,0.2405,0.2367,0.0088</t>
+  </si>
+  <si>
+    <t>0.9804,0.0068,0.0053,0.0013</t>
+  </si>
+  <si>
+    <t>0.9540,0.0261,0.0185,0.0025</t>
+  </si>
+  <si>
+    <t>0.0598,0.8847,0.1082,0.0102</t>
+  </si>
+  <si>
+    <t>0.7624,0.1840,0.0530,0.0096</t>
+  </si>
+  <si>
+    <t>0.9388,0.0115,0.0727,0.0013</t>
+  </si>
+  <si>
+    <t>0.9927,0.0028,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0022,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0006,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9948,0.0039,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9881,0.0015,0.0005,0.0073</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9621,0.0677,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.1555,0.9089,0.0040,0.0002</t>
+  </si>
+  <si>
+    <t>0.6668,0.4317,0.0058,0.0044</t>
+  </si>
+  <si>
+    <t>0.9783,0.0120,0.0061,0.0019</t>
+  </si>
+  <si>
+    <t>0.9947,0.0071,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9016,0.1067,0.0184,0.0054</t>
+  </si>
+  <si>
+    <t>0.9955,0.0027,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9701,0.0562,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.0329,0.9973,0.0010</t>
+  </si>
+  <si>
+    <t>0.9548,0.0339,0.0098,0.0025</t>
+  </si>
+  <si>
+    <t>0.0009,0.0154,0.9965,0.0005</t>
+  </si>
+  <si>
+    <t>0.0054,0.0395,0.9894,0.0028</t>
+  </si>
+  <si>
+    <t>0.0763,0.0048,0.9465,0.0043</t>
+  </si>
+  <si>
+    <t>0.0155,0.1642,0.9507,0.0081</t>
+  </si>
+  <si>
+    <t>0.0018,0.0052,0.9948,0.0008</t>
+  </si>
+  <si>
+    <t>0.0078,0.0019,0.9891,0.0010</t>
+  </si>
+  <si>
+    <t>0.0029,0.0014,0.9949,0.0007</t>
+  </si>
+  <si>
+    <t>0.0357,0.0041,0.9586,0.0049</t>
+  </si>
+  <si>
+    <t>0.5080,0.0080,0.6395,0.0038</t>
+  </si>
+  <si>
+    <t>0.6635,0.0523,0.3689,0.0088</t>
+  </si>
+  <si>
+    <t>0.1505,0.0776,0.8218,0.0022</t>
+  </si>
+  <si>
+    <t>0.1372,0.3045,0.5886,0.0047</t>
+  </si>
+  <si>
+    <t>0.5791,0.0317,0.4764,0.0103</t>
+  </si>
+  <si>
+    <t>0.3418,0.0352,0.6763,0.0233</t>
+  </si>
+  <si>
+    <t>0.0445,0.0074,0.9565,0.0057</t>
+  </si>
+  <si>
+    <t>0.8799,0.2562,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9578,0.0752,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9656,0.0824,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9695,0.0770,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9872,0.0343,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9498,0.0062,0.0372,0.0022</t>
+  </si>
+  <si>
+    <t>0.8873,0.0028,0.1533,0.0029</t>
+  </si>
+  <si>
+    <t>0.4797,0.0036,0.2326,0.1130</t>
+  </si>
+  <si>
+    <t>0.9144,0.0011,0.1747,0.0004</t>
+  </si>
+  <si>
+    <t>0.6062,0.0031,0.2130,0.0527</t>
+  </si>
+  <si>
+    <t>0.0054,0.0064,0.9817,0.0418</t>
+  </si>
+  <si>
+    <t>0.0111,0.0132,0.9750,0.0077</t>
+  </si>
+  <si>
+    <t>0.0225,0.0366,0.9805,0.0020</t>
+  </si>
+  <si>
+    <t>0.1070,0.0055,0.8900,0.0060</t>
+  </si>
+  <si>
+    <t>0.0110,0.3821,0.6619,0.0105</t>
+  </si>
+  <si>
+    <t>0.9958,0.0018,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0065,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0032,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0046,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0025,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9928,0.0071,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0061,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.1074,0.0523,0.9244,0.0123</t>
+  </si>
+  <si>
+    <t>0.0420,0.0752,0.8660,0.0169</t>
+  </si>
+  <si>
+    <t>0.7053,0.0781,0.2213,0.0225</t>
+  </si>
+  <si>
+    <t>0.0036,0.0045,0.9924,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.0082,0.9749,0.0086</t>
+  </si>
+  <si>
+    <t>0.0333,0.0346,0.9244,0.0022</t>
+  </si>
+  <si>
+    <t>0.0111,0.0009,0.9929,0.0002</t>
+  </si>
+  <si>
+    <t>0.0186,0.0022,0.9719,0.0022</t>
+  </si>
+  <si>
+    <t>0.0043,0.0157,0.9911,0.0028</t>
+  </si>
+  <si>
+    <t>0.0105,0.0177,0.9819,0.0049</t>
+  </si>
+  <si>
+    <t>0.0147,0.0283,0.9605,0.0046</t>
+  </si>
+  <si>
+    <t>0.9780,0.0003,0.0176,0.0008</t>
+  </si>
+  <si>
+    <t>0.9359,0.0011,0.1056,0.0016</t>
+  </si>
+  <si>
+    <t>0.9678,0.0020,0.0211,0.0021</t>
+  </si>
+  <si>
+    <t>0.9863,0.0170,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0030,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0012,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9967,0.0037,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0018,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0153,0.0181,0.9558,0.0020</t>
+  </si>
+  <si>
+    <t>0.0061,0.0207,0.9796,0.0101</t>
+  </si>
+  <si>
+    <t>0.0400,0.0258,0.9211,0.0038</t>
+  </si>
+  <si>
+    <t>0.0729,0.0564,0.8765,0.0075</t>
+  </si>
+  <si>
+    <t>0.0121,0.0068,0.9853,0.0007</t>
+  </si>
+  <si>
+    <t>0.0728,0.0035,0.8650,0.0512</t>
+  </si>
+  <si>
+    <t>0.2452,0.0275,0.7453,0.0251</t>
+  </si>
+  <si>
+    <t>0.0183,0.0037,0.9261,0.0254</t>
+  </si>
+  <si>
+    <t>0.8400,0.0029,0.0061,0.1664</t>
+  </si>
+  <si>
+    <t>0.0036,0.0177,0.0002,0.9962</t>
+  </si>
+  <si>
+    <t>0.2298,0.0008,0.0002,0.9222</t>
+  </si>
+  <si>
+    <t>0.0019,0.0002,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0022,0.0007,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.9227,0.0114,0.0120,0.0278</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1964,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1992,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2121,7 +2118,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2135,7 +2132,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2160,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2216,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2230,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2244,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2272,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2286,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2401,7 +2398,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2415,7 +2412,7 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>297</v>
@@ -2429,7 +2426,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2443,7 +2440,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2468,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2496,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2569,7 +2566,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2580,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2594,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2608,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2622,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2636,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2692,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2849,7 +2846,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2874,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2916,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2944,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2958,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3042,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3056,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3070,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3098,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3140,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3154,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3244,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3353,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3367,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3406,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3434,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3448,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3462,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3476,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3490,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3504,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,10 +3518,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3535,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3560,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3574,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3591,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3602,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3616,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3630,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3644,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3658,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3672,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3759,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3826,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3840,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3910,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3938,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3952,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3980,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4022,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4078,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4190,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4358,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4375,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4512,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4540,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4582,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4624,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4638,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4655,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4666,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4680,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4781,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4809,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4834,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4876,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4991,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5016,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5030,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5086,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5114,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5156,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5324,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5366,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5394,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5408,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5450,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5464,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5478,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5492,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
